--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8655,0.0844,0.0459,0.0041</t>
-  </si>
-  <si>
-    <t>0.7263,0.0996,0.1610,0.0379</t>
-  </si>
-  <si>
-    <t>0.8022,0.0938,0.0941,0.0111</t>
-  </si>
-  <si>
-    <t>0.8805,0.0478,0.0319,0.0180</t>
-  </si>
-  <si>
-    <t>0.5957,0.4227,0.0319,0.0056</t>
-  </si>
-  <si>
-    <t>0.6201,0.3531,0.0241,0.0058</t>
-  </si>
-  <si>
-    <t>0.5048,0.4946,0.0509,0.0047</t>
-  </si>
-  <si>
-    <t>0.6752,0.3464,0.0200,0.0031</t>
-  </si>
-  <si>
-    <t>0.6951,0.3104,0.0121,0.0038</t>
-  </si>
-  <si>
-    <t>0.6576,0.3325,0.0087,0.0029</t>
-  </si>
-  <si>
-    <t>0.6125,0.3368,0.0418,0.0063</t>
-  </si>
-  <si>
-    <t>0.4749,0.5774,0.0292,0.0034</t>
-  </si>
-  <si>
-    <t>0.8859,0.0448,0.1147,0.0029</t>
-  </si>
-  <si>
-    <t>0.9470,0.0114,0.0438,0.0025</t>
-  </si>
-  <si>
-    <t>0.8432,0.0234,0.2343,0.0095</t>
-  </si>
-  <si>
-    <t>0.9172,0.0129,0.1046,0.0039</t>
-  </si>
-  <si>
-    <t>0.8203,0.1141,0.0755,0.0055</t>
-  </si>
-  <si>
-    <t>0.3976,0.6737,0.0188,0.0004</t>
-  </si>
-  <si>
-    <t>0.3832,0.6382,0.0679,0.0021</t>
-  </si>
-  <si>
-    <t>0.6340,0.3947,0.0277,0.0016</t>
-  </si>
-  <si>
-    <t>0.4399,0.5809,0.0494,0.0024</t>
-  </si>
-  <si>
-    <t>0.3534,0.6906,0.0522,0.0019</t>
-  </si>
-  <si>
-    <t>0.9672,0.0034,0.0427,0.0011</t>
-  </si>
-  <si>
-    <t>0.9440,0.0029,0.1112,0.0009</t>
-  </si>
-  <si>
-    <t>0.8569,0.0057,0.2805,0.0024</t>
-  </si>
-  <si>
-    <t>0.7330,0.0479,0.2741,0.0018</t>
-  </si>
-  <si>
-    <t>0.3391,0.0950,0.7105,0.0083</t>
-  </si>
-  <si>
-    <t>0.5100,0.0159,0.6815,0.0037</t>
-  </si>
-  <si>
-    <t>0.6555,0.0121,0.5031,0.0052</t>
-  </si>
-  <si>
-    <t>0.8023,0.1516,0.0455,0.0066</t>
-  </si>
-  <si>
-    <t>0.6466,0.2883,0.1162,0.0089</t>
-  </si>
-  <si>
-    <t>0.0093,0.4973,0.9769,0.0025</t>
-  </si>
-  <si>
-    <t>0.3792,0.4069,0.2179,0.0029</t>
-  </si>
-  <si>
-    <t>0.8275,0.1173,0.0451,0.0062</t>
-  </si>
-  <si>
-    <t>0.6146,0.2883,0.1080,0.0137</t>
-  </si>
-  <si>
-    <t>0.9367,0.0317,0.0049,0.0027</t>
-  </si>
-  <si>
-    <t>0.5291,0.4065,0.1165,0.0054</t>
-  </si>
-  <si>
-    <t>0.2695,0.0173,0.7877,0.0087</t>
-  </si>
-  <si>
-    <t>0.9550,0.0003,0.1543,0.0003</t>
-  </si>
-  <si>
-    <t>0.8124,0.0024,0.4081,0.0015</t>
-  </si>
-  <si>
-    <t>0.6315,0.0059,0.5996,0.0044</t>
-  </si>
-  <si>
-    <t>0.6874,0.0024,0.5907,0.0012</t>
-  </si>
-  <si>
-    <t>0.1845,0.0587,0.6305,0.0007</t>
-  </si>
-  <si>
-    <t>0.8534,0.0072,0.3311,0.0013</t>
-  </si>
-  <si>
-    <t>0.9117,0.0217,0.0660,0.0063</t>
-  </si>
-  <si>
-    <t>0.8349,0.0999,0.0411,0.0015</t>
-  </si>
-  <si>
-    <t>0.8314,0.0573,0.1179,0.0017</t>
-  </si>
-  <si>
-    <t>0.8372,0.0931,0.0503,0.0008</t>
-  </si>
-  <si>
-    <t>0.0454,0.0294,0.9612,0.0042</t>
-  </si>
-  <si>
-    <t>0.1212,0.1333,0.8109,0.0027</t>
-  </si>
-  <si>
-    <t>0.7598,0.0064,0.4692,0.0017</t>
-  </si>
-  <si>
-    <t>0.8868,0.0157,0.1564,0.0045</t>
-  </si>
-  <si>
-    <t>0.7345,0.0132,0.3659,0.0034</t>
-  </si>
-  <si>
-    <t>0.1558,0.0094,0.9256,0.0008</t>
-  </si>
-  <si>
-    <t>0.4757,0.5291,0.0569,0.0059</t>
-  </si>
-  <si>
-    <t>0.5056,0.4812,0.0947,0.0107</t>
-  </si>
-  <si>
-    <t>0.8059,0.1236,0.0173,0.0098</t>
-  </si>
-  <si>
-    <t>0.0418,0.3490,0.8609,0.0061</t>
-  </si>
-  <si>
-    <t>0.7782,0.1894,0.0132,0.0057</t>
-  </si>
-  <si>
-    <t>0.5831,0.4443,0.0310,0.0052</t>
-  </si>
-  <si>
-    <t>0.7030,0.2739,0.0149,0.0044</t>
-  </si>
-  <si>
-    <t>0.1215,0.0389,0.9122,0.0025</t>
-  </si>
-  <si>
-    <t>0.2110,0.0184,0.8932,0.0018</t>
-  </si>
-  <si>
-    <t>0.1897,0.0155,0.8716,0.0033</t>
-  </si>
-  <si>
-    <t>0.0397,0.0824,0.9546,0.0012</t>
-  </si>
-  <si>
-    <t>0.4008,0.0069,0.7919,0.0022</t>
-  </si>
-  <si>
-    <t>0.6525,0.2695,0.0876,0.0012</t>
-  </si>
-  <si>
-    <t>0.0140,0.9500,0.1871,0.0002</t>
-  </si>
-  <si>
-    <t>0.8260,0.1260,0.0587,0.0043</t>
-  </si>
-  <si>
-    <t>0.6794,0.2350,0.1083,0.0141</t>
-  </si>
-  <si>
-    <t>0.0921,0.0767,0.9087,0.0117</t>
-  </si>
-  <si>
-    <t>0.0627,0.2192,0.7953,0.0014</t>
-  </si>
-  <si>
-    <t>0.0486,0.4440,0.9140,0.0010</t>
-  </si>
-  <si>
-    <t>0.1967,0.3025,0.5929,0.0031</t>
-  </si>
-  <si>
-    <t>0.0138,0.2141,0.9756,0.0008</t>
-  </si>
-  <si>
-    <t>0.8445,0.0727,0.0377,0.0202</t>
-  </si>
-  <si>
-    <t>0.9148,0.0213,0.0258,0.0209</t>
-  </si>
-  <si>
-    <t>0.7973,0.0283,0.0734,0.0776</t>
-  </si>
-  <si>
-    <t>0.8145,0.0693,0.0383,0.0473</t>
-  </si>
-  <si>
-    <t>0.8570,0.0455,0.0931,0.0178</t>
-  </si>
-  <si>
-    <t>0.8030,0.0345,0.0321,0.0909</t>
-  </si>
-  <si>
-    <t>0.2798,0.0601,0.7311,0.0018</t>
-  </si>
-  <si>
-    <t>0.3306,0.0335,0.7159,0.0031</t>
-  </si>
-  <si>
-    <t>0.2286,0.0207,0.8480,0.0018</t>
-  </si>
-  <si>
-    <t>0.7415,0.0076,0.5090,0.0024</t>
-  </si>
-  <si>
-    <t>0.4362,0.0149,0.7289,0.0013</t>
-  </si>
-  <si>
-    <t>0.5550,0.0183,0.5352,0.0010</t>
-  </si>
-  <si>
-    <t>0.4415,0.6057,0.0528,0.0043</t>
-  </si>
-  <si>
-    <t>0.7262,0.2634,0.0115,0.0035</t>
-  </si>
-  <si>
-    <t>0.7916,0.1563,0.0432,0.0068</t>
-  </si>
-  <si>
-    <t>0.3607,0.6679,0.0284,0.0045</t>
-  </si>
-  <si>
-    <t>0.8302,0.1452,0.0108,0.0035</t>
-  </si>
-  <si>
-    <t>0.5345,0.4391,0.0354,0.0036</t>
-  </si>
-  <si>
-    <t>0.2733,0.7458,0.0678,0.0026</t>
-  </si>
-  <si>
-    <t>0.5595,0.4581,0.0264,0.0048</t>
-  </si>
-  <si>
-    <t>0.5252,0.4782,0.0427,0.0048</t>
-  </si>
-  <si>
-    <t>0.5533,0.4856,0.0256,0.0057</t>
-  </si>
-  <si>
-    <t>0.4571,0.5401,0.0551,0.0059</t>
-  </si>
-  <si>
-    <t>0.5696,0.4670,0.0296,0.0040</t>
-  </si>
-  <si>
-    <t>0.7720,0.1480,0.0094,0.0088</t>
-  </si>
-  <si>
-    <t>0.6506,0.3888,0.0142,0.0033</t>
-  </si>
-  <si>
-    <t>0.7424,0.1926,0.0130,0.0062</t>
-  </si>
-  <si>
-    <t>0.6428,0.3489,0.0280,0.0057</t>
-  </si>
-  <si>
-    <t>0.1618,0.1059,0.8790,0.0032</t>
-  </si>
-  <si>
-    <t>0.9261,0.0104,0.0943,0.0037</t>
-  </si>
-  <si>
-    <t>0.8484,0.0176,0.2026,0.0117</t>
-  </si>
-  <si>
-    <t>0.8623,0.0266,0.1789,0.0076</t>
-  </si>
-  <si>
-    <t>0.0780,0.9189,0.0386,0.0015</t>
-  </si>
-  <si>
-    <t>0.1432,0.8541,0.0656,0.0014</t>
-  </si>
-  <si>
-    <t>0.0722,0.9290,0.0348,0.0008</t>
-  </si>
-  <si>
-    <t>0.3190,0.7054,0.0676,0.0042</t>
-  </si>
-  <si>
-    <t>0.3454,0.6588,0.0544,0.0036</t>
-  </si>
-  <si>
-    <t>0.0188,0.9752,0.0183,0.0004</t>
-  </si>
-  <si>
-    <t>0.1544,0.8493,0.0493,0.0015</t>
-  </si>
-  <si>
-    <t>0.9602,0.0096,0.0258,0.0025</t>
-  </si>
-  <si>
-    <t>0.8658,0.0285,0.1663,0.0094</t>
-  </si>
-  <si>
-    <t>0.8862,0.0419,0.0568,0.0043</t>
-  </si>
-  <si>
-    <t>0.8620,0.0464,0.1191,0.0073</t>
-  </si>
-  <si>
-    <t>0.8038,0.1211,0.0719,0.0103</t>
-  </si>
-  <si>
-    <t>0.7724,0.1473,0.0499,0.0006</t>
-  </si>
-  <si>
-    <t>0.7765,0.0645,0.1713,0.0011</t>
-  </si>
-  <si>
-    <t>0.5726,0.4299,0.0458,0.0031</t>
-  </si>
-  <si>
-    <t>0.2120,0.2815,0.4883,0.0112</t>
-  </si>
-  <si>
-    <t>0.2917,0.7116,0.0559,0.0008</t>
-  </si>
-  <si>
-    <t>0.7760,0.2181,0.0234,0.0018</t>
-  </si>
-  <si>
-    <t>0.7566,0.2393,0.0221,0.0033</t>
-  </si>
-  <si>
-    <t>0.3785,0.5247,0.2268,0.0157</t>
-  </si>
-  <si>
-    <t>0.7564,0.2085,0.0121,0.0031</t>
-  </si>
-  <si>
-    <t>0.5136,0.4954,0.0627,0.0081</t>
-  </si>
-  <si>
-    <t>0.6775,0.2664,0.0414,0.0089</t>
-  </si>
-  <si>
-    <t>0.8274,0.1798,0.0102,0.0026</t>
-  </si>
-  <si>
-    <t>0.5073,0.5125,0.0444,0.0060</t>
-  </si>
-  <si>
-    <t>0.7649,0.1854,0.0431,0.0075</t>
-  </si>
-  <si>
-    <t>0.2400,0.7273,0.1151,0.0111</t>
-  </si>
-  <si>
-    <t>0.2385,0.0082,0.8620,0.0042</t>
-  </si>
-  <si>
-    <t>0.1967,0.0160,0.8991,0.0025</t>
-  </si>
-  <si>
-    <t>0.2681,0.0120,0.8585,0.0024</t>
-  </si>
-  <si>
-    <t>0.8539,0.0050,0.3342,0.0025</t>
-  </si>
-  <si>
-    <t>0.9252,0.0329,0.0434,0.0030</t>
-  </si>
-  <si>
-    <t>0.8593,0.0929,0.0457,0.0035</t>
-  </si>
-  <si>
-    <t>0.6606,0.0531,0.3950,0.0039</t>
-  </si>
-  <si>
-    <t>0.7693,0.0920,0.1988,0.0173</t>
-  </si>
-  <si>
-    <t>0.8373,0.0345,0.0268,0.0498</t>
-  </si>
-  <si>
-    <t>0.8394,0.0079,0.0239,0.1197</t>
-  </si>
-  <si>
-    <t>0.9401,0.0097,0.0169,0.0154</t>
-  </si>
-  <si>
-    <t>0.7451,0.1101,0.0960,0.0502</t>
-  </si>
-  <si>
-    <t>0.0484,0.4697,0.6361,0.0024</t>
-  </si>
-  <si>
-    <t>0.8973,0.0520,0.0054,0.0061</t>
-  </si>
-  <si>
-    <t>0.5430,0.4564,0.0495,0.0042</t>
-  </si>
-  <si>
-    <t>0.7469,0.2799,0.0137,0.0025</t>
-  </si>
-  <si>
-    <t>0.3852,0.6327,0.0551,0.0048</t>
-  </si>
-  <si>
-    <t>0.5799,0.3929,0.0788,0.0036</t>
-  </si>
-  <si>
-    <t>0.7430,0.1726,0.0895,0.0178</t>
-  </si>
-  <si>
-    <t>0.5590,0.3446,0.0672,0.0312</t>
-  </si>
-  <si>
-    <t>0.1320,0.0940,0.8604,0.0302</t>
-  </si>
-  <si>
-    <t>0.8916,0.0444,0.0377,0.0110</t>
-  </si>
-  <si>
-    <t>0.3664,0.5651,0.0580,0.0199</t>
-  </si>
-  <si>
-    <t>0.8290,0.1235,0.0326,0.0048</t>
-  </si>
-  <si>
-    <t>0.7040,0.2579,0.0561,0.0041</t>
-  </si>
-  <si>
-    <t>0.7361,0.2283,0.0438,0.0038</t>
-  </si>
-  <si>
-    <t>0.6864,0.2206,0.0782,0.0079</t>
-  </si>
-  <si>
-    <t>0.6496,0.2848,0.0548,0.0020</t>
-  </si>
-  <si>
-    <t>0.6877,0.2493,0.0558,0.0099</t>
-  </si>
-  <si>
-    <t>0.5412,0.4465,0.0411,0.0053</t>
-  </si>
-  <si>
-    <t>0.7914,0.1593,0.0203,0.0086</t>
-  </si>
-  <si>
-    <t>0.5541,0.4075,0.0675,0.0112</t>
-  </si>
-  <si>
-    <t>0.6803,0.2918,0.0331,0.0048</t>
-  </si>
-  <si>
-    <t>0.8465,0.1168,0.0122,0.0052</t>
-  </si>
-  <si>
-    <t>0.5914,0.3498,0.0703,0.0147</t>
-  </si>
-  <si>
-    <t>0.7772,0.1811,0.0186,0.0067</t>
-  </si>
-  <si>
-    <t>0.6917,0.3411,0.0193,0.0031</t>
-  </si>
-  <si>
-    <t>0.7948,0.2174,0.0273,0.0014</t>
-  </si>
-  <si>
-    <t>0.6235,0.4007,0.0249,0.0025</t>
-  </si>
-  <si>
-    <t>0.3473,0.6655,0.0382,0.0049</t>
-  </si>
-  <si>
-    <t>0.5912,0.2859,0.1823,0.0077</t>
-  </si>
-  <si>
-    <t>0.7658,0.2465,0.0117,0.0017</t>
-  </si>
-  <si>
-    <t>0.7223,0.2068,0.0460,0.0084</t>
-  </si>
-  <si>
-    <t>0.6839,0.3708,0.0145,0.0039</t>
-  </si>
-  <si>
-    <t>0.6367,0.3675,0.0367,0.0048</t>
-  </si>
-  <si>
-    <t>0.0527,0.1522,0.9311,0.0023</t>
-  </si>
-  <si>
-    <t>0.7773,0.2074,0.0288,0.0045</t>
-  </si>
-  <si>
-    <t>0.2801,0.0065,0.8073,0.0046</t>
-  </si>
-  <si>
-    <t>0.2374,0.0152,0.8775,0.0029</t>
-  </si>
-  <si>
-    <t>0.5631,0.0436,0.6010,0.0055</t>
-  </si>
-  <si>
-    <t>0.0233,0.0051,0.9898,0.0006</t>
-  </si>
-  <si>
-    <t>0.6346,0.0090,0.5733,0.0037</t>
-  </si>
-  <si>
-    <t>0.0785,0.0361,0.9444,0.0011</t>
-  </si>
-  <si>
-    <t>0.3049,0.0993,0.7246,0.0103</t>
-  </si>
-  <si>
-    <t>0.9169,0.0217,0.0601,0.0077</t>
-  </si>
-  <si>
-    <t>0.7032,0.0872,0.3790,0.0198</t>
-  </si>
-  <si>
-    <t>0.5913,0.2770,0.1744,0.0098</t>
-  </si>
-  <si>
-    <t>0.7449,0.1389,0.1217,0.0033</t>
-  </si>
-  <si>
-    <t>0.7064,0.1821,0.0727,0.0021</t>
-  </si>
-  <si>
-    <t>0.7870,0.1251,0.0949,0.0067</t>
-  </si>
-  <si>
-    <t>0.7537,0.1494,0.1347,0.0120</t>
-  </si>
-  <si>
-    <t>0.7144,0.1235,0.1952,0.0047</t>
-  </si>
-  <si>
-    <t>0.3386,0.7046,0.0661,0.0042</t>
-  </si>
-  <si>
-    <t>0.1804,0.8286,0.0558,0.0021</t>
-  </si>
-  <si>
-    <t>0.5931,0.4439,0.0337,0.0041</t>
-  </si>
-  <si>
-    <t>0.6738,0.3832,0.0134,0.0030</t>
-  </si>
-  <si>
-    <t>0.6609,0.3546,0.0216,0.0034</t>
-  </si>
-  <si>
-    <t>0.8499,0.0557,0.1175,0.0045</t>
-  </si>
-  <si>
-    <t>0.9123,0.0331,0.0406,0.0048</t>
-  </si>
-  <si>
-    <t>0.7705,0.1357,0.1114,0.0052</t>
-  </si>
-  <si>
-    <t>0.8663,0.0425,0.1210,0.0068</t>
-  </si>
-  <si>
-    <t>0.9160,0.0155,0.0813,0.0040</t>
-  </si>
-  <si>
-    <t>0.4437,0.0434,0.6785,0.0145</t>
-  </si>
-  <si>
-    <t>0.9065,0.0048,0.1844,0.0031</t>
-  </si>
-  <si>
-    <t>0.9479,0.0020,0.1386,0.0008</t>
-  </si>
-  <si>
-    <t>0.8440,0.0055,0.3640,0.0008</t>
-  </si>
-  <si>
-    <t>0.8849,0.0090,0.1782,0.0038</t>
-  </si>
-  <si>
-    <t>0.6991,0.2556,0.0291,0.0081</t>
-  </si>
-  <si>
-    <t>0.4040,0.6775,0.0244,0.0031</t>
-  </si>
-  <si>
-    <t>0.3755,0.6499,0.0823,0.0073</t>
-  </si>
-  <si>
-    <t>0.6049,0.4024,0.0227,0.0063</t>
-  </si>
-  <si>
-    <t>0.6048,0.3971,0.0482,0.0087</t>
-  </si>
-  <si>
-    <t>0.6028,0.3464,0.0100,0.0042</t>
-  </si>
-  <si>
-    <t>0.5525,0.4126,0.0440,0.0072</t>
-  </si>
-  <si>
-    <t>0.5881,0.4720,0.0294,0.0033</t>
-  </si>
-  <si>
-    <t>0.5017,0.2678,0.4308,0.0728</t>
-  </si>
-  <si>
-    <t>0.6182,0.2993,0.1094,0.0049</t>
-  </si>
-  <si>
-    <t>0.8856,0.0724,0.0355,0.0076</t>
-  </si>
-  <si>
-    <t>0.0637,0.1111,0.9346,0.0030</t>
-  </si>
-  <si>
-    <t>0.0056,0.0186,0.9824,0.0046</t>
-  </si>
-  <si>
-    <t>0.4818,0.0473,0.6160,0.0151</t>
-  </si>
-  <si>
-    <t>0.0223,0.0169,0.9865,0.0011</t>
-  </si>
-  <si>
-    <t>0.2149,0.0241,0.8190,0.0094</t>
-  </si>
-  <si>
-    <t>0.0051,0.0058,0.9887,0.0036</t>
-  </si>
-  <si>
-    <t>0.6973,0.0074,0.5331,0.0040</t>
-  </si>
-  <si>
-    <t>0.8422,0.0623,0.0911,0.0079</t>
-  </si>
-  <si>
-    <t>0.8564,0.0535,0.1208,0.0026</t>
-  </si>
-  <si>
-    <t>0.8593,0.0303,0.1495,0.0066</t>
-  </si>
-  <si>
-    <t>0.8596,0.0574,0.0843,0.0065</t>
-  </si>
-  <si>
-    <t>0.3683,0.6488,0.0311,0.0042</t>
-  </si>
-  <si>
-    <t>0.7423,0.2922,0.0091,0.0017</t>
-  </si>
-  <si>
-    <t>0.4472,0.5961,0.0347,0.0043</t>
-  </si>
-  <si>
-    <t>0.8075,0.1460,0.0145,0.0068</t>
-  </si>
-  <si>
-    <t>0.8853,0.0751,0.0115,0.0058</t>
-  </si>
-  <si>
-    <t>0.6933,0.3136,0.0152,0.0041</t>
-  </si>
-  <si>
-    <t>0.5465,0.4613,0.0304,0.0051</t>
-  </si>
-  <si>
-    <t>0.8022,0.1162,0.0172,0.0128</t>
-  </si>
-  <si>
-    <t>0.7124,0.0524,0.3823,0.0086</t>
-  </si>
-  <si>
-    <t>0.1486,0.0424,0.9133,0.0014</t>
-  </si>
-  <si>
-    <t>0.0702,0.0206,0.9342,0.0077</t>
-  </si>
-  <si>
-    <t>0.8781,0.0124,0.1885,0.0047</t>
-  </si>
-  <si>
-    <t>0.2816,0.0149,0.8072,0.0061</t>
-  </si>
-  <si>
-    <t>0.6906,0.0147,0.3863,0.0080</t>
-  </si>
-  <si>
-    <t>0.8755,0.0135,0.1863,0.0052</t>
-  </si>
-  <si>
-    <t>0.9616,0.0011,0.0833,0.0009</t>
-  </si>
-  <si>
-    <t>0.7910,0.1423,0.0247,0.0108</t>
-  </si>
-  <si>
-    <t>0.8225,0.0855,0.0812,0.0140</t>
-  </si>
-  <si>
-    <t>0.9352,0.0032,0.0023,0.0561</t>
-  </si>
-  <si>
-    <t>0.7614,0.0094,0.0231,0.2091</t>
-  </si>
-  <si>
-    <t>0.7589,0.0839,0.1503,0.0487</t>
-  </si>
-  <si>
-    <t>0.8995,0.0251,0.0531,0.0110</t>
+    <t>0.9311,0.0408,0.0147,0.0024</t>
+  </si>
+  <si>
+    <t>0.7504,0.0453,0.0430,0.1292</t>
+  </si>
+  <si>
+    <t>0.6731,0.2987,0.0649,0.0039</t>
+  </si>
+  <si>
+    <t>0.8806,0.0149,0.0243,0.0481</t>
+  </si>
+  <si>
+    <t>0.6169,0.3724,0.0477,0.0079</t>
+  </si>
+  <si>
+    <t>0.5934,0.3893,0.0218,0.0071</t>
+  </si>
+  <si>
+    <t>0.4884,0.4815,0.0662,0.0102</t>
+  </si>
+  <si>
+    <t>0.4710,0.5102,0.0662,0.0068</t>
+  </si>
+  <si>
+    <t>0.8415,0.1446,0.0127,0.0033</t>
+  </si>
+  <si>
+    <t>0.6639,0.3789,0.0189,0.0037</t>
+  </si>
+  <si>
+    <t>0.6577,0.2369,0.0235,0.0104</t>
+  </si>
+  <si>
+    <t>0.3127,0.7231,0.0568,0.0040</t>
+  </si>
+  <si>
+    <t>0.8674,0.0349,0.1292,0.0104</t>
+  </si>
+  <si>
+    <t>0.8861,0.0200,0.1576,0.0027</t>
+  </si>
+  <si>
+    <t>0.7003,0.0583,0.3872,0.0059</t>
+  </si>
+  <si>
+    <t>0.5358,0.1176,0.4488,0.0074</t>
+  </si>
+  <si>
+    <t>0.6043,0.3093,0.1057,0.0055</t>
+  </si>
+  <si>
+    <t>0.3396,0.6907,0.0306,0.0007</t>
+  </si>
+  <si>
+    <t>0.2164,0.7970,0.0366,0.0008</t>
+  </si>
+  <si>
+    <t>0.5420,0.4767,0.0358,0.0037</t>
+  </si>
+  <si>
+    <t>0.5332,0.5275,0.0278,0.0013</t>
+  </si>
+  <si>
+    <t>0.1681,0.8378,0.0829,0.0020</t>
+  </si>
+  <si>
+    <t>0.9264,0.0115,0.0811,0.0048</t>
+  </si>
+  <si>
+    <t>0.7000,0.0141,0.4558,0.0057</t>
+  </si>
+  <si>
+    <t>0.7303,0.0149,0.4690,0.0030</t>
+  </si>
+  <si>
+    <t>0.9227,0.0161,0.0967,0.0023</t>
+  </si>
+  <si>
+    <t>0.9208,0.0107,0.1144,0.0032</t>
+  </si>
+  <si>
+    <t>0.8076,0.0140,0.3085,0.0069</t>
+  </si>
+  <si>
+    <t>0.5168,0.0053,0.6065,0.0063</t>
+  </si>
+  <si>
+    <t>0.8895,0.1060,0.0194,0.0018</t>
+  </si>
+  <si>
+    <t>0.4916,0.5300,0.0411,0.0027</t>
+  </si>
+  <si>
+    <t>0.0058,0.2477,0.9717,0.0107</t>
+  </si>
+  <si>
+    <t>0.1212,0.7819,0.1552,0.0010</t>
+  </si>
+  <si>
+    <t>0.6393,0.2987,0.0829,0.0111</t>
+  </si>
+  <si>
+    <t>0.7437,0.1771,0.0464,0.0085</t>
+  </si>
+  <si>
+    <t>0.4769,0.5594,0.0473,0.0028</t>
+  </si>
+  <si>
+    <t>0.8326,0.1443,0.0244,0.0023</t>
+  </si>
+  <si>
+    <t>0.2707,0.0245,0.8603,0.0022</t>
+  </si>
+  <si>
+    <t>0.8260,0.0017,0.4497,0.0012</t>
+  </si>
+  <si>
+    <t>0.8911,0.0021,0.2403,0.0022</t>
+  </si>
+  <si>
+    <t>0.8523,0.0022,0.2783,0.0032</t>
+  </si>
+  <si>
+    <t>0.9057,0.0037,0.2140,0.0017</t>
+  </si>
+  <si>
+    <t>0.2906,0.1965,0.3659,0.0043</t>
+  </si>
+  <si>
+    <t>0.7690,0.0050,0.4592,0.0021</t>
+  </si>
+  <si>
+    <t>0.7908,0.1620,0.0566,0.0040</t>
+  </si>
+  <si>
+    <t>0.8517,0.0588,0.0942,0.0017</t>
+  </si>
+  <si>
+    <t>0.8312,0.0580,0.1155,0.0016</t>
+  </si>
+  <si>
+    <t>0.7753,0.1539,0.0567,0.0016</t>
+  </si>
+  <si>
+    <t>0.1150,0.0059,0.9438,0.0022</t>
+  </si>
+  <si>
+    <t>0.1489,0.0181,0.8960,0.0029</t>
+  </si>
+  <si>
+    <t>0.4538,0.0155,0.6947,0.0091</t>
+  </si>
+  <si>
+    <t>0.3381,0.0699,0.7014,0.0162</t>
+  </si>
+  <si>
+    <t>0.0537,0.0450,0.9550,0.0041</t>
+  </si>
+  <si>
+    <t>0.3309,0.0077,0.8453,0.0008</t>
+  </si>
+  <si>
+    <t>0.7933,0.1447,0.0118,0.0049</t>
+  </si>
+  <si>
+    <t>0.7494,0.2069,0.0163,0.0062</t>
+  </si>
+  <si>
+    <t>0.7091,0.2272,0.0293,0.0089</t>
+  </si>
+  <si>
+    <t>0.3217,0.5077,0.2184,0.0036</t>
+  </si>
+  <si>
+    <t>0.8468,0.1356,0.0131,0.0037</t>
+  </si>
+  <si>
+    <t>0.3636,0.6669,0.0286,0.0031</t>
+  </si>
+  <si>
+    <t>0.7112,0.2263,0.0224,0.0071</t>
+  </si>
+  <si>
+    <t>0.0452,0.2589,0.9521,0.0038</t>
+  </si>
+  <si>
+    <t>0.0245,0.0113,0.9839,0.0012</t>
+  </si>
+  <si>
+    <t>0.1230,0.0074,0.9083,0.0020</t>
+  </si>
+  <si>
+    <t>0.0508,0.0784,0.9265,0.0024</t>
+  </si>
+  <si>
+    <t>0.1647,0.0126,0.9308,0.0012</t>
+  </si>
+  <si>
+    <t>0.2677,0.6717,0.0785,0.0013</t>
+  </si>
+  <si>
+    <t>0.0662,0.9210,0.0176,0.0008</t>
+  </si>
+  <si>
+    <t>0.8340,0.1174,0.0460,0.0015</t>
+  </si>
+  <si>
+    <t>0.7446,0.1627,0.0703,0.0076</t>
+  </si>
+  <si>
+    <t>0.0555,0.4118,0.9191,0.0179</t>
+  </si>
+  <si>
+    <t>0.3997,0.0590,0.6594,0.0022</t>
+  </si>
+  <si>
+    <t>0.6150,0.0147,0.5899,0.0018</t>
+  </si>
+  <si>
+    <t>0.2808,0.1012,0.6442,0.0045</t>
+  </si>
+  <si>
+    <t>0.0873,0.1556,0.8443,0.0014</t>
+  </si>
+  <si>
+    <t>0.8915,0.0325,0.0300,0.0190</t>
+  </si>
+  <si>
+    <t>0.8366,0.0296,0.0352,0.0731</t>
+  </si>
+  <si>
+    <t>0.8296,0.0331,0.0461,0.0783</t>
+  </si>
+  <si>
+    <t>0.7505,0.0965,0.0697,0.0588</t>
+  </si>
+  <si>
+    <t>0.9477,0.0132,0.0307,0.0082</t>
+  </si>
+  <si>
+    <t>0.8957,0.0277,0.0416,0.0172</t>
+  </si>
+  <si>
+    <t>0.4008,0.0812,0.7016,0.0050</t>
+  </si>
+  <si>
+    <t>0.0520,0.0208,0.9682,0.0005</t>
+  </si>
+  <si>
+    <t>0.2364,0.0098,0.9077,0.0006</t>
+  </si>
+  <si>
+    <t>0.3441,0.0201,0.8215,0.0013</t>
+  </si>
+  <si>
+    <t>0.2582,0.0348,0.8135,0.0015</t>
+  </si>
+  <si>
+    <t>0.6239,0.0439,0.2716,0.0008</t>
+  </si>
+  <si>
+    <t>0.6084,0.3834,0.0245,0.0059</t>
+  </si>
+  <si>
+    <t>0.5870,0.4090,0.0460,0.0089</t>
+  </si>
+  <si>
+    <t>0.5891,0.4513,0.0127,0.0022</t>
+  </si>
+  <si>
+    <t>0.6666,0.3773,0.0151,0.0026</t>
+  </si>
+  <si>
+    <t>0.6214,0.4386,0.0218,0.0020</t>
+  </si>
+  <si>
+    <t>0.5706,0.4168,0.0295,0.0031</t>
+  </si>
+  <si>
+    <t>0.6984,0.3049,0.0087,0.0021</t>
+  </si>
+  <si>
+    <t>0.8766,0.0881,0.0110,0.0033</t>
+  </si>
+  <si>
+    <t>0.6937,0.3438,0.0118,0.0016</t>
+  </si>
+  <si>
+    <t>0.8364,0.1321,0.0183,0.0061</t>
+  </si>
+  <si>
+    <t>0.8773,0.0710,0.0087,0.0049</t>
+  </si>
+  <si>
+    <t>0.5833,0.4632,0.0277,0.0030</t>
+  </si>
+  <si>
+    <t>0.7595,0.2065,0.0118,0.0057</t>
+  </si>
+  <si>
+    <t>0.3547,0.6907,0.0427,0.0031</t>
+  </si>
+  <si>
+    <t>0.8408,0.1413,0.0172,0.0038</t>
+  </si>
+  <si>
+    <t>0.7377,0.2401,0.0165,0.0049</t>
+  </si>
+  <si>
+    <t>0.0168,0.1295,0.9803,0.0009</t>
+  </si>
+  <si>
+    <t>0.2869,0.0168,0.7933,0.0038</t>
+  </si>
+  <si>
+    <t>0.9525,0.0068,0.0308,0.0045</t>
+  </si>
+  <si>
+    <t>0.8880,0.0168,0.1635,0.0075</t>
+  </si>
+  <si>
+    <t>0.0766,0.9262,0.0406,0.0011</t>
+  </si>
+  <si>
+    <t>0.3605,0.6916,0.0346,0.0017</t>
+  </si>
+  <si>
+    <t>0.4178,0.6152,0.0482,0.0026</t>
+  </si>
+  <si>
+    <t>0.4953,0.5612,0.0362,0.0016</t>
+  </si>
+  <si>
+    <t>0.5324,0.5205,0.0245,0.0014</t>
+  </si>
+  <si>
+    <t>0.0192,0.9792,0.0096,0.0005</t>
+  </si>
+  <si>
+    <t>0.5578,0.4824,0.0450,0.0029</t>
+  </si>
+  <si>
+    <t>0.8006,0.1059,0.0886,0.0077</t>
+  </si>
+  <si>
+    <t>0.8207,0.0120,0.2429,0.0085</t>
+  </si>
+  <si>
+    <t>0.7089,0.1385,0.2154,0.0186</t>
+  </si>
+  <si>
+    <t>0.8361,0.0660,0.1356,0.0045</t>
+  </si>
+  <si>
+    <t>0.8509,0.0466,0.1380,0.0068</t>
+  </si>
+  <si>
+    <t>0.5457,0.3926,0.0568,0.0008</t>
+  </si>
+  <si>
+    <t>0.6987,0.1699,0.1127,0.0023</t>
+  </si>
+  <si>
+    <t>0.7542,0.1810,0.0687,0.0038</t>
+  </si>
+  <si>
+    <t>0.4223,0.1755,0.2842,0.0024</t>
+  </si>
+  <si>
+    <t>0.8837,0.1030,0.0129,0.0009</t>
+  </si>
+  <si>
+    <t>0.7760,0.2127,0.0190,0.0032</t>
+  </si>
+  <si>
+    <t>0.4708,0.5045,0.0989,0.0055</t>
+  </si>
+  <si>
+    <t>0.8480,0.1432,0.0116,0.0041</t>
+  </si>
+  <si>
+    <t>0.5968,0.4143,0.0369,0.0040</t>
+  </si>
+  <si>
+    <t>0.6642,0.3493,0.0270,0.0034</t>
+  </si>
+  <si>
+    <t>0.6554,0.3192,0.0384,0.0066</t>
+  </si>
+  <si>
+    <t>0.4717,0.5446,0.0492,0.0068</t>
+  </si>
+  <si>
+    <t>0.6741,0.2871,0.0583,0.0058</t>
+  </si>
+  <si>
+    <t>0.7765,0.1899,0.0241,0.0043</t>
+  </si>
+  <si>
+    <t>0.5274,0.5089,0.0265,0.0025</t>
+  </si>
+  <si>
+    <t>0.0528,0.0716,0.9608,0.0038</t>
+  </si>
+  <si>
+    <t>0.3261,0.0152,0.7898,0.0013</t>
+  </si>
+  <si>
+    <t>0.2095,0.0131,0.8801,0.0013</t>
+  </si>
+  <si>
+    <t>0.6688,0.0097,0.5544,0.0028</t>
+  </si>
+  <si>
+    <t>0.9360,0.0109,0.0653,0.0028</t>
+  </si>
+  <si>
+    <t>0.8289,0.0886,0.0790,0.0074</t>
+  </si>
+  <si>
+    <t>0.8279,0.0438,0.2016,0.0069</t>
+  </si>
+  <si>
+    <t>0.8188,0.0801,0.1120,0.0068</t>
+  </si>
+  <si>
+    <t>0.8505,0.0367,0.0435,0.0472</t>
+  </si>
+  <si>
+    <t>0.6552,0.0126,0.0554,0.2711</t>
+  </si>
+  <si>
+    <t>0.9104,0.0214,0.0530,0.0145</t>
+  </si>
+  <si>
+    <t>0.8336,0.0353,0.0541,0.0584</t>
+  </si>
+  <si>
+    <t>0.0356,0.7972,0.3968,0.0011</t>
+  </si>
+  <si>
+    <t>0.8116,0.1801,0.0214,0.0037</t>
+  </si>
+  <si>
+    <t>0.2489,0.7264,0.0828,0.0076</t>
+  </si>
+  <si>
+    <t>0.6261,0.4009,0.0139,0.0023</t>
+  </si>
+  <si>
+    <t>0.3126,0.6960,0.0776,0.0033</t>
+  </si>
+  <si>
+    <t>0.4046,0.5485,0.1287,0.0089</t>
+  </si>
+  <si>
+    <t>0.6676,0.2521,0.0633,0.0090</t>
+  </si>
+  <si>
+    <t>0.8102,0.1451,0.0165,0.0071</t>
+  </si>
+  <si>
+    <t>0.1536,0.2013,0.8237,0.0177</t>
+  </si>
+  <si>
+    <t>0.9230,0.0229,0.0130,0.0099</t>
+  </si>
+  <si>
+    <t>0.5846,0.3422,0.0668,0.0155</t>
+  </si>
+  <si>
+    <t>0.6037,0.3547,0.0932,0.0124</t>
+  </si>
+  <si>
+    <t>0.7333,0.1605,0.0930,0.0187</t>
+  </si>
+  <si>
+    <t>0.7739,0.1731,0.0319,0.0061</t>
+  </si>
+  <si>
+    <t>0.5294,0.4840,0.0513,0.0034</t>
+  </si>
+  <si>
+    <t>0.8438,0.1189,0.0316,0.0025</t>
+  </si>
+  <si>
+    <t>0.6617,0.3024,0.0598,0.0016</t>
+  </si>
+  <si>
+    <t>0.7457,0.1690,0.0330,0.0119</t>
+  </si>
+  <si>
+    <t>0.3717,0.6498,0.0842,0.0049</t>
+  </si>
+  <si>
+    <t>0.4773,0.5393,0.0563,0.0062</t>
+  </si>
+  <si>
+    <t>0.7196,0.2353,0.0332,0.0095</t>
+  </si>
+  <si>
+    <t>0.8184,0.1272,0.0448,0.0107</t>
+  </si>
+  <si>
+    <t>0.6852,0.3230,0.0272,0.0039</t>
+  </si>
+  <si>
+    <t>0.6676,0.3552,0.0228,0.0048</t>
+  </si>
+  <si>
+    <t>0.5860,0.3482,0.0876,0.0100</t>
+  </si>
+  <si>
+    <t>0.3684,0.6319,0.0583,0.0026</t>
+  </si>
+  <si>
+    <t>0.2573,0.7403,0.0584,0.0022</t>
+  </si>
+  <si>
+    <t>0.4539,0.5251,0.0634,0.0091</t>
+  </si>
+  <si>
+    <t>0.6285,0.2762,0.1147,0.0099</t>
+  </si>
+  <si>
+    <t>0.3884,0.6402,0.0335,0.0029</t>
+  </si>
+  <si>
+    <t>0.5086,0.4509,0.0697,0.0055</t>
+  </si>
+  <si>
+    <t>0.7102,0.2358,0.0269,0.0079</t>
+  </si>
+  <si>
+    <t>0.7539,0.2332,0.0195,0.0029</t>
+  </si>
+  <si>
+    <t>0.0411,0.5047,0.8989,0.0040</t>
+  </si>
+  <si>
+    <t>0.3293,0.6523,0.0945,0.0111</t>
+  </si>
+  <si>
+    <t>0.3578,0.0139,0.7822,0.0031</t>
+  </si>
+  <si>
+    <t>0.4356,0.0015,0.7130,0.0033</t>
+  </si>
+  <si>
+    <t>0.7038,0.0604,0.2787,0.0056</t>
+  </si>
+  <si>
+    <t>0.0559,0.0257,0.9699,0.0022</t>
+  </si>
+  <si>
+    <t>0.0116,0.0431,0.9843,0.0019</t>
+  </si>
+  <si>
+    <t>0.2883,0.0394,0.7517,0.0089</t>
+  </si>
+  <si>
+    <t>0.3729,0.0088,0.7915,0.0024</t>
+  </si>
+  <si>
+    <t>0.8285,0.0650,0.1487,0.0054</t>
+  </si>
+  <si>
+    <t>0.8235,0.0760,0.1203,0.0033</t>
+  </si>
+  <si>
+    <t>0.9539,0.0116,0.0337,0.0017</t>
+  </si>
+  <si>
+    <t>0.8286,0.0701,0.1301,0.0029</t>
+  </si>
+  <si>
+    <t>0.7177,0.1253,0.1936,0.0054</t>
+  </si>
+  <si>
+    <t>0.8866,0.0479,0.0616,0.0030</t>
+  </si>
+  <si>
+    <t>0.6952,0.0798,0.3051,0.0348</t>
+  </si>
+  <si>
+    <t>0.8219,0.0592,0.1718,0.0053</t>
+  </si>
+  <si>
+    <t>0.3518,0.6761,0.0570,0.0034</t>
+  </si>
+  <si>
+    <t>0.2244,0.8064,0.0395,0.0021</t>
+  </si>
+  <si>
+    <t>0.0436,0.9545,0.0372,0.0020</t>
+  </si>
+  <si>
+    <t>0.7785,0.1668,0.0205,0.0064</t>
+  </si>
+  <si>
+    <t>0.4870,0.5715,0.0469,0.0037</t>
+  </si>
+  <si>
+    <t>0.6113,0.1783,0.1673,0.0023</t>
+  </si>
+  <si>
+    <t>0.8742,0.0500,0.0993,0.0032</t>
+  </si>
+  <si>
+    <t>0.7776,0.0991,0.1546,0.0044</t>
+  </si>
+  <si>
+    <t>0.9674,0.0043,0.0254,0.0032</t>
+  </si>
+  <si>
+    <t>0.7433,0.1143,0.1838,0.0059</t>
+  </si>
+  <si>
+    <t>0.4817,0.0807,0.5515,0.0126</t>
+  </si>
+  <si>
+    <t>0.8645,0.0035,0.2796,0.0030</t>
+  </si>
+  <si>
+    <t>0.8353,0.0061,0.3513,0.0038</t>
+  </si>
+  <si>
+    <t>0.6922,0.0069,0.5483,0.0014</t>
+  </si>
+  <si>
+    <t>0.8824,0.0024,0.2752,0.0007</t>
+  </si>
+  <si>
+    <t>0.5836,0.4403,0.0249,0.0044</t>
+  </si>
+  <si>
+    <t>0.8073,0.1420,0.0147,0.0069</t>
+  </si>
+  <si>
+    <t>0.5391,0.4736,0.0454,0.0053</t>
+  </si>
+  <si>
+    <t>0.5160,0.4866,0.0360,0.0062</t>
+  </si>
+  <si>
+    <t>0.7364,0.2474,0.0185,0.0041</t>
+  </si>
+  <si>
+    <t>0.2564,0.7755,0.0312,0.0041</t>
+  </si>
+  <si>
+    <t>0.7197,0.2980,0.0108,0.0027</t>
+  </si>
+  <si>
+    <t>0.4752,0.5163,0.0713,0.0080</t>
+  </si>
+  <si>
+    <t>0.3992,0.4458,0.3909,0.0304</t>
+  </si>
+  <si>
+    <t>0.6129,0.3284,0.1218,0.0089</t>
+  </si>
+  <si>
+    <t>0.5781,0.4035,0.0615,0.0075</t>
+  </si>
+  <si>
+    <t>0.3879,0.0076,0.7872,0.0020</t>
+  </si>
+  <si>
+    <t>0.2228,0.0094,0.8796,0.0018</t>
+  </si>
+  <si>
+    <t>0.5710,0.0735,0.5346,0.0095</t>
+  </si>
+  <si>
+    <t>0.0411,0.0076,0.9767,0.0008</t>
+  </si>
+  <si>
+    <t>0.8996,0.0133,0.1483,0.0037</t>
+  </si>
+  <si>
+    <t>0.0975,0.0093,0.9115,0.0031</t>
+  </si>
+  <si>
+    <t>0.6314,0.0133,0.5233,0.0080</t>
+  </si>
+  <si>
+    <t>0.0307,0.2080,0.9215,0.0049</t>
+  </si>
+  <si>
+    <t>0.9252,0.0195,0.0555,0.0029</t>
+  </si>
+  <si>
+    <t>0.9033,0.0122,0.1132,0.0041</t>
+  </si>
+  <si>
+    <t>0.9247,0.0245,0.0602,0.0028</t>
+  </si>
+  <si>
+    <t>0.6544,0.3239,0.0140,0.0033</t>
+  </si>
+  <si>
+    <t>0.2602,0.7665,0.0717,0.0063</t>
+  </si>
+  <si>
+    <t>0.8292,0.0813,0.0071,0.0077</t>
+  </si>
+  <si>
+    <t>0.6739,0.3914,0.0249,0.0030</t>
+  </si>
+  <si>
+    <t>0.7020,0.2678,0.0254,0.0043</t>
+  </si>
+  <si>
+    <t>0.6118,0.3802,0.0250,0.0041</t>
+  </si>
+  <si>
+    <t>0.5913,0.4677,0.0183,0.0027</t>
+  </si>
+  <si>
+    <t>0.6762,0.3496,0.0239,0.0033</t>
+  </si>
+  <si>
+    <t>0.7723,0.0224,0.3489,0.0065</t>
+  </si>
+  <si>
+    <t>0.0583,0.0164,0.9600,0.0012</t>
+  </si>
+  <si>
+    <t>0.0721,0.0057,0.9565,0.0026</t>
+  </si>
+  <si>
+    <t>0.6872,0.0074,0.5098,0.0035</t>
+  </si>
+  <si>
+    <t>0.7895,0.0042,0.4070,0.0016</t>
+  </si>
+  <si>
+    <t>0.4299,0.0376,0.6612,0.0199</t>
+  </si>
+  <si>
+    <t>0.6631,0.0307,0.4182,0.0113</t>
+  </si>
+  <si>
+    <t>0.8992,0.0041,0.2164,0.0027</t>
+  </si>
+  <si>
+    <t>0.9141,0.0392,0.0169,0.0051</t>
+  </si>
+  <si>
+    <t>0.9071,0.0224,0.0553,0.0107</t>
+  </si>
+  <si>
+    <t>0.9362,0.0147,0.0269,0.0114</t>
+  </si>
+  <si>
+    <t>0.8617,0.0266,0.0367,0.0435</t>
+  </si>
+  <si>
+    <t>0.6140,0.0985,0.1273,0.2026</t>
+  </si>
+  <si>
+    <t>0.7480,0.1357,0.1028,0.0192</t>
   </si>
 </sst>
 </file>
@@ -2051,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D9" t="s">
         <v>271</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2709,7 +2709,7 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D56" t="s">
         <v>318</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2779,7 +2779,7 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D61" t="s">
         <v>323</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3171,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D89" t="s">
         <v>351</v>
@@ -3213,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D92" t="s">
         <v>354</v>
@@ -3255,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
         <v>357</v>
@@ -3311,7 +3311,7 @@
         <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D99" t="s">
         <v>361</v>
@@ -3353,7 +3353,7 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D102" t="s">
         <v>364</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3717,7 +3717,7 @@
         <v>259</v>
       </c>
       <c r="C128" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D128" t="s">
         <v>390</v>
@@ -3773,7 +3773,7 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D132" t="s">
         <v>394</v>
@@ -3787,7 +3787,7 @@
         <v>259</v>
       </c>
       <c r="C133" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D133" t="s">
         <v>395</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4067,7 +4067,7 @@
         <v>259</v>
       </c>
       <c r="C153" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D153" t="s">
         <v>415</v>
@@ -4137,7 +4137,7 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
         <v>420</v>
@@ -4249,7 +4249,7 @@
         <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D166" t="s">
         <v>428</v>
@@ -4263,7 +4263,7 @@
         <v>259</v>
       </c>
       <c r="C167" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D167" t="s">
         <v>429</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4403,7 +4403,7 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D177" t="s">
         <v>439</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4473,7 +4473,7 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D182" t="s">
         <v>444</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4921,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D214" t="s">
         <v>476</v>
@@ -4935,7 +4935,7 @@
         <v>259</v>
       </c>
       <c r="C215" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D215" t="s">
         <v>477</v>
@@ -4977,7 +4977,7 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D218" t="s">
         <v>480</v>
@@ -5005,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D220" t="s">
         <v>482</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5215,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D235" t="s">
         <v>497</v>
@@ -5229,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D236" t="s">
         <v>498</v>
@@ -5243,7 +5243,7 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D237" t="s">
         <v>499</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9311,0.0408,0.0147,0.0024</t>
-  </si>
-  <si>
-    <t>0.7504,0.0453,0.0430,0.1292</t>
-  </si>
-  <si>
-    <t>0.6731,0.2987,0.0649,0.0039</t>
-  </si>
-  <si>
-    <t>0.8806,0.0149,0.0243,0.0481</t>
-  </si>
-  <si>
-    <t>0.6169,0.3724,0.0477,0.0079</t>
-  </si>
-  <si>
-    <t>0.5934,0.3893,0.0218,0.0071</t>
-  </si>
-  <si>
-    <t>0.4884,0.4815,0.0662,0.0102</t>
-  </si>
-  <si>
-    <t>0.4710,0.5102,0.0662,0.0068</t>
-  </si>
-  <si>
-    <t>0.8415,0.1446,0.0127,0.0033</t>
-  </si>
-  <si>
-    <t>0.6639,0.3789,0.0189,0.0037</t>
-  </si>
-  <si>
-    <t>0.6577,0.2369,0.0235,0.0104</t>
-  </si>
-  <si>
-    <t>0.3127,0.7231,0.0568,0.0040</t>
-  </si>
-  <si>
-    <t>0.8674,0.0349,0.1292,0.0104</t>
-  </si>
-  <si>
-    <t>0.8861,0.0200,0.1576,0.0027</t>
-  </si>
-  <si>
-    <t>0.7003,0.0583,0.3872,0.0059</t>
-  </si>
-  <si>
-    <t>0.5358,0.1176,0.4488,0.0074</t>
-  </si>
-  <si>
-    <t>0.6043,0.3093,0.1057,0.0055</t>
-  </si>
-  <si>
-    <t>0.3396,0.6907,0.0306,0.0007</t>
-  </si>
-  <si>
-    <t>0.2164,0.7970,0.0366,0.0008</t>
-  </si>
-  <si>
-    <t>0.5420,0.4767,0.0358,0.0037</t>
-  </si>
-  <si>
-    <t>0.5332,0.5275,0.0278,0.0013</t>
-  </si>
-  <si>
-    <t>0.1681,0.8378,0.0829,0.0020</t>
-  </si>
-  <si>
-    <t>0.9264,0.0115,0.0811,0.0048</t>
-  </si>
-  <si>
-    <t>0.7000,0.0141,0.4558,0.0057</t>
-  </si>
-  <si>
-    <t>0.7303,0.0149,0.4690,0.0030</t>
-  </si>
-  <si>
-    <t>0.9227,0.0161,0.0967,0.0023</t>
-  </si>
-  <si>
-    <t>0.9208,0.0107,0.1144,0.0032</t>
-  </si>
-  <si>
-    <t>0.8076,0.0140,0.3085,0.0069</t>
-  </si>
-  <si>
-    <t>0.5168,0.0053,0.6065,0.0063</t>
-  </si>
-  <si>
-    <t>0.8895,0.1060,0.0194,0.0018</t>
-  </si>
-  <si>
-    <t>0.4916,0.5300,0.0411,0.0027</t>
-  </si>
-  <si>
-    <t>0.0058,0.2477,0.9717,0.0107</t>
-  </si>
-  <si>
-    <t>0.1212,0.7819,0.1552,0.0010</t>
-  </si>
-  <si>
-    <t>0.6393,0.2987,0.0829,0.0111</t>
-  </si>
-  <si>
-    <t>0.7437,0.1771,0.0464,0.0085</t>
-  </si>
-  <si>
-    <t>0.4769,0.5594,0.0473,0.0028</t>
-  </si>
-  <si>
-    <t>0.8326,0.1443,0.0244,0.0023</t>
-  </si>
-  <si>
-    <t>0.2707,0.0245,0.8603,0.0022</t>
-  </si>
-  <si>
-    <t>0.8260,0.0017,0.4497,0.0012</t>
-  </si>
-  <si>
-    <t>0.8911,0.0021,0.2403,0.0022</t>
-  </si>
-  <si>
-    <t>0.8523,0.0022,0.2783,0.0032</t>
-  </si>
-  <si>
-    <t>0.9057,0.0037,0.2140,0.0017</t>
-  </si>
-  <si>
-    <t>0.2906,0.1965,0.3659,0.0043</t>
-  </si>
-  <si>
-    <t>0.7690,0.0050,0.4592,0.0021</t>
-  </si>
-  <si>
-    <t>0.7908,0.1620,0.0566,0.0040</t>
-  </si>
-  <si>
-    <t>0.8517,0.0588,0.0942,0.0017</t>
-  </si>
-  <si>
-    <t>0.8312,0.0580,0.1155,0.0016</t>
-  </si>
-  <si>
-    <t>0.7753,0.1539,0.0567,0.0016</t>
-  </si>
-  <si>
-    <t>0.1150,0.0059,0.9438,0.0022</t>
-  </si>
-  <si>
-    <t>0.1489,0.0181,0.8960,0.0029</t>
-  </si>
-  <si>
-    <t>0.4538,0.0155,0.6947,0.0091</t>
-  </si>
-  <si>
-    <t>0.3381,0.0699,0.7014,0.0162</t>
-  </si>
-  <si>
-    <t>0.0537,0.0450,0.9550,0.0041</t>
-  </si>
-  <si>
-    <t>0.3309,0.0077,0.8453,0.0008</t>
-  </si>
-  <si>
-    <t>0.7933,0.1447,0.0118,0.0049</t>
-  </si>
-  <si>
-    <t>0.7494,0.2069,0.0163,0.0062</t>
-  </si>
-  <si>
-    <t>0.7091,0.2272,0.0293,0.0089</t>
-  </si>
-  <si>
-    <t>0.3217,0.5077,0.2184,0.0036</t>
-  </si>
-  <si>
-    <t>0.8468,0.1356,0.0131,0.0037</t>
-  </si>
-  <si>
-    <t>0.3636,0.6669,0.0286,0.0031</t>
-  </si>
-  <si>
-    <t>0.7112,0.2263,0.0224,0.0071</t>
-  </si>
-  <si>
-    <t>0.0452,0.2589,0.9521,0.0038</t>
-  </si>
-  <si>
-    <t>0.0245,0.0113,0.9839,0.0012</t>
-  </si>
-  <si>
-    <t>0.1230,0.0074,0.9083,0.0020</t>
-  </si>
-  <si>
-    <t>0.0508,0.0784,0.9265,0.0024</t>
-  </si>
-  <si>
-    <t>0.1647,0.0126,0.9308,0.0012</t>
-  </si>
-  <si>
-    <t>0.2677,0.6717,0.0785,0.0013</t>
-  </si>
-  <si>
-    <t>0.0662,0.9210,0.0176,0.0008</t>
-  </si>
-  <si>
-    <t>0.8340,0.1174,0.0460,0.0015</t>
-  </si>
-  <si>
-    <t>0.7446,0.1627,0.0703,0.0076</t>
-  </si>
-  <si>
-    <t>0.0555,0.4118,0.9191,0.0179</t>
-  </si>
-  <si>
-    <t>0.3997,0.0590,0.6594,0.0022</t>
-  </si>
-  <si>
-    <t>0.6150,0.0147,0.5899,0.0018</t>
-  </si>
-  <si>
-    <t>0.2808,0.1012,0.6442,0.0045</t>
-  </si>
-  <si>
-    <t>0.0873,0.1556,0.8443,0.0014</t>
-  </si>
-  <si>
-    <t>0.8915,0.0325,0.0300,0.0190</t>
-  </si>
-  <si>
-    <t>0.8366,0.0296,0.0352,0.0731</t>
-  </si>
-  <si>
-    <t>0.8296,0.0331,0.0461,0.0783</t>
-  </si>
-  <si>
-    <t>0.7505,0.0965,0.0697,0.0588</t>
-  </si>
-  <si>
-    <t>0.9477,0.0132,0.0307,0.0082</t>
-  </si>
-  <si>
-    <t>0.8957,0.0277,0.0416,0.0172</t>
-  </si>
-  <si>
-    <t>0.4008,0.0812,0.7016,0.0050</t>
-  </si>
-  <si>
-    <t>0.0520,0.0208,0.9682,0.0005</t>
-  </si>
-  <si>
-    <t>0.2364,0.0098,0.9077,0.0006</t>
-  </si>
-  <si>
-    <t>0.3441,0.0201,0.8215,0.0013</t>
-  </si>
-  <si>
-    <t>0.2582,0.0348,0.8135,0.0015</t>
-  </si>
-  <si>
-    <t>0.6239,0.0439,0.2716,0.0008</t>
-  </si>
-  <si>
-    <t>0.6084,0.3834,0.0245,0.0059</t>
-  </si>
-  <si>
-    <t>0.5870,0.4090,0.0460,0.0089</t>
-  </si>
-  <si>
-    <t>0.5891,0.4513,0.0127,0.0022</t>
-  </si>
-  <si>
-    <t>0.6666,0.3773,0.0151,0.0026</t>
-  </si>
-  <si>
-    <t>0.6214,0.4386,0.0218,0.0020</t>
-  </si>
-  <si>
-    <t>0.5706,0.4168,0.0295,0.0031</t>
-  </si>
-  <si>
-    <t>0.6984,0.3049,0.0087,0.0021</t>
-  </si>
-  <si>
-    <t>0.8766,0.0881,0.0110,0.0033</t>
-  </si>
-  <si>
-    <t>0.6937,0.3438,0.0118,0.0016</t>
-  </si>
-  <si>
-    <t>0.8364,0.1321,0.0183,0.0061</t>
-  </si>
-  <si>
-    <t>0.8773,0.0710,0.0087,0.0049</t>
-  </si>
-  <si>
-    <t>0.5833,0.4632,0.0277,0.0030</t>
-  </si>
-  <si>
-    <t>0.7595,0.2065,0.0118,0.0057</t>
-  </si>
-  <si>
-    <t>0.3547,0.6907,0.0427,0.0031</t>
-  </si>
-  <si>
-    <t>0.8408,0.1413,0.0172,0.0038</t>
-  </si>
-  <si>
-    <t>0.7377,0.2401,0.0165,0.0049</t>
-  </si>
-  <si>
-    <t>0.0168,0.1295,0.9803,0.0009</t>
-  </si>
-  <si>
-    <t>0.2869,0.0168,0.7933,0.0038</t>
-  </si>
-  <si>
-    <t>0.9525,0.0068,0.0308,0.0045</t>
-  </si>
-  <si>
-    <t>0.8880,0.0168,0.1635,0.0075</t>
-  </si>
-  <si>
-    <t>0.0766,0.9262,0.0406,0.0011</t>
-  </si>
-  <si>
-    <t>0.3605,0.6916,0.0346,0.0017</t>
-  </si>
-  <si>
-    <t>0.4178,0.6152,0.0482,0.0026</t>
-  </si>
-  <si>
-    <t>0.4953,0.5612,0.0362,0.0016</t>
-  </si>
-  <si>
-    <t>0.5324,0.5205,0.0245,0.0014</t>
-  </si>
-  <si>
-    <t>0.0192,0.9792,0.0096,0.0005</t>
-  </si>
-  <si>
-    <t>0.5578,0.4824,0.0450,0.0029</t>
-  </si>
-  <si>
-    <t>0.8006,0.1059,0.0886,0.0077</t>
-  </si>
-  <si>
-    <t>0.8207,0.0120,0.2429,0.0085</t>
-  </si>
-  <si>
-    <t>0.7089,0.1385,0.2154,0.0186</t>
-  </si>
-  <si>
-    <t>0.8361,0.0660,0.1356,0.0045</t>
-  </si>
-  <si>
-    <t>0.8509,0.0466,0.1380,0.0068</t>
-  </si>
-  <si>
-    <t>0.5457,0.3926,0.0568,0.0008</t>
-  </si>
-  <si>
-    <t>0.6987,0.1699,0.1127,0.0023</t>
-  </si>
-  <si>
-    <t>0.7542,0.1810,0.0687,0.0038</t>
-  </si>
-  <si>
-    <t>0.4223,0.1755,0.2842,0.0024</t>
-  </si>
-  <si>
-    <t>0.8837,0.1030,0.0129,0.0009</t>
-  </si>
-  <si>
-    <t>0.7760,0.2127,0.0190,0.0032</t>
-  </si>
-  <si>
-    <t>0.4708,0.5045,0.0989,0.0055</t>
-  </si>
-  <si>
-    <t>0.8480,0.1432,0.0116,0.0041</t>
-  </si>
-  <si>
-    <t>0.5968,0.4143,0.0369,0.0040</t>
-  </si>
-  <si>
-    <t>0.6642,0.3493,0.0270,0.0034</t>
-  </si>
-  <si>
-    <t>0.6554,0.3192,0.0384,0.0066</t>
-  </si>
-  <si>
-    <t>0.4717,0.5446,0.0492,0.0068</t>
-  </si>
-  <si>
-    <t>0.6741,0.2871,0.0583,0.0058</t>
-  </si>
-  <si>
-    <t>0.7765,0.1899,0.0241,0.0043</t>
-  </si>
-  <si>
-    <t>0.5274,0.5089,0.0265,0.0025</t>
-  </si>
-  <si>
-    <t>0.0528,0.0716,0.9608,0.0038</t>
-  </si>
-  <si>
-    <t>0.3261,0.0152,0.7898,0.0013</t>
-  </si>
-  <si>
-    <t>0.2095,0.0131,0.8801,0.0013</t>
-  </si>
-  <si>
-    <t>0.6688,0.0097,0.5544,0.0028</t>
-  </si>
-  <si>
-    <t>0.9360,0.0109,0.0653,0.0028</t>
-  </si>
-  <si>
-    <t>0.8289,0.0886,0.0790,0.0074</t>
-  </si>
-  <si>
-    <t>0.8279,0.0438,0.2016,0.0069</t>
-  </si>
-  <si>
-    <t>0.8188,0.0801,0.1120,0.0068</t>
-  </si>
-  <si>
-    <t>0.8505,0.0367,0.0435,0.0472</t>
-  </si>
-  <si>
-    <t>0.6552,0.0126,0.0554,0.2711</t>
-  </si>
-  <si>
-    <t>0.9104,0.0214,0.0530,0.0145</t>
-  </si>
-  <si>
-    <t>0.8336,0.0353,0.0541,0.0584</t>
-  </si>
-  <si>
-    <t>0.0356,0.7972,0.3968,0.0011</t>
-  </si>
-  <si>
-    <t>0.8116,0.1801,0.0214,0.0037</t>
-  </si>
-  <si>
-    <t>0.2489,0.7264,0.0828,0.0076</t>
-  </si>
-  <si>
-    <t>0.6261,0.4009,0.0139,0.0023</t>
-  </si>
-  <si>
-    <t>0.3126,0.6960,0.0776,0.0033</t>
-  </si>
-  <si>
-    <t>0.4046,0.5485,0.1287,0.0089</t>
-  </si>
-  <si>
-    <t>0.6676,0.2521,0.0633,0.0090</t>
-  </si>
-  <si>
-    <t>0.8102,0.1451,0.0165,0.0071</t>
-  </si>
-  <si>
-    <t>0.1536,0.2013,0.8237,0.0177</t>
-  </si>
-  <si>
-    <t>0.9230,0.0229,0.0130,0.0099</t>
-  </si>
-  <si>
-    <t>0.5846,0.3422,0.0668,0.0155</t>
-  </si>
-  <si>
-    <t>0.6037,0.3547,0.0932,0.0124</t>
-  </si>
-  <si>
-    <t>0.7333,0.1605,0.0930,0.0187</t>
-  </si>
-  <si>
-    <t>0.7739,0.1731,0.0319,0.0061</t>
-  </si>
-  <si>
-    <t>0.5294,0.4840,0.0513,0.0034</t>
-  </si>
-  <si>
-    <t>0.8438,0.1189,0.0316,0.0025</t>
-  </si>
-  <si>
-    <t>0.6617,0.3024,0.0598,0.0016</t>
-  </si>
-  <si>
-    <t>0.7457,0.1690,0.0330,0.0119</t>
-  </si>
-  <si>
-    <t>0.3717,0.6498,0.0842,0.0049</t>
-  </si>
-  <si>
-    <t>0.4773,0.5393,0.0563,0.0062</t>
-  </si>
-  <si>
-    <t>0.7196,0.2353,0.0332,0.0095</t>
-  </si>
-  <si>
-    <t>0.8184,0.1272,0.0448,0.0107</t>
-  </si>
-  <si>
-    <t>0.6852,0.3230,0.0272,0.0039</t>
-  </si>
-  <si>
-    <t>0.6676,0.3552,0.0228,0.0048</t>
-  </si>
-  <si>
-    <t>0.5860,0.3482,0.0876,0.0100</t>
-  </si>
-  <si>
-    <t>0.3684,0.6319,0.0583,0.0026</t>
-  </si>
-  <si>
-    <t>0.2573,0.7403,0.0584,0.0022</t>
-  </si>
-  <si>
-    <t>0.4539,0.5251,0.0634,0.0091</t>
-  </si>
-  <si>
-    <t>0.6285,0.2762,0.1147,0.0099</t>
-  </si>
-  <si>
-    <t>0.3884,0.6402,0.0335,0.0029</t>
-  </si>
-  <si>
-    <t>0.5086,0.4509,0.0697,0.0055</t>
-  </si>
-  <si>
-    <t>0.7102,0.2358,0.0269,0.0079</t>
-  </si>
-  <si>
-    <t>0.7539,0.2332,0.0195,0.0029</t>
-  </si>
-  <si>
-    <t>0.0411,0.5047,0.8989,0.0040</t>
-  </si>
-  <si>
-    <t>0.3293,0.6523,0.0945,0.0111</t>
-  </si>
-  <si>
-    <t>0.3578,0.0139,0.7822,0.0031</t>
-  </si>
-  <si>
-    <t>0.4356,0.0015,0.7130,0.0033</t>
-  </si>
-  <si>
-    <t>0.7038,0.0604,0.2787,0.0056</t>
-  </si>
-  <si>
-    <t>0.0559,0.0257,0.9699,0.0022</t>
-  </si>
-  <si>
-    <t>0.0116,0.0431,0.9843,0.0019</t>
-  </si>
-  <si>
-    <t>0.2883,0.0394,0.7517,0.0089</t>
-  </si>
-  <si>
-    <t>0.3729,0.0088,0.7915,0.0024</t>
-  </si>
-  <si>
-    <t>0.8285,0.0650,0.1487,0.0054</t>
-  </si>
-  <si>
-    <t>0.8235,0.0760,0.1203,0.0033</t>
-  </si>
-  <si>
-    <t>0.9539,0.0116,0.0337,0.0017</t>
-  </si>
-  <si>
-    <t>0.8286,0.0701,0.1301,0.0029</t>
-  </si>
-  <si>
-    <t>0.7177,0.1253,0.1936,0.0054</t>
-  </si>
-  <si>
-    <t>0.8866,0.0479,0.0616,0.0030</t>
-  </si>
-  <si>
-    <t>0.6952,0.0798,0.3051,0.0348</t>
-  </si>
-  <si>
-    <t>0.8219,0.0592,0.1718,0.0053</t>
-  </si>
-  <si>
-    <t>0.3518,0.6761,0.0570,0.0034</t>
-  </si>
-  <si>
-    <t>0.2244,0.8064,0.0395,0.0021</t>
-  </si>
-  <si>
-    <t>0.0436,0.9545,0.0372,0.0020</t>
-  </si>
-  <si>
-    <t>0.7785,0.1668,0.0205,0.0064</t>
-  </si>
-  <si>
-    <t>0.4870,0.5715,0.0469,0.0037</t>
-  </si>
-  <si>
-    <t>0.6113,0.1783,0.1673,0.0023</t>
-  </si>
-  <si>
-    <t>0.8742,0.0500,0.0993,0.0032</t>
-  </si>
-  <si>
-    <t>0.7776,0.0991,0.1546,0.0044</t>
-  </si>
-  <si>
-    <t>0.9674,0.0043,0.0254,0.0032</t>
-  </si>
-  <si>
-    <t>0.7433,0.1143,0.1838,0.0059</t>
-  </si>
-  <si>
-    <t>0.4817,0.0807,0.5515,0.0126</t>
-  </si>
-  <si>
-    <t>0.8645,0.0035,0.2796,0.0030</t>
-  </si>
-  <si>
-    <t>0.8353,0.0061,0.3513,0.0038</t>
-  </si>
-  <si>
-    <t>0.6922,0.0069,0.5483,0.0014</t>
-  </si>
-  <si>
-    <t>0.8824,0.0024,0.2752,0.0007</t>
-  </si>
-  <si>
-    <t>0.5836,0.4403,0.0249,0.0044</t>
-  </si>
-  <si>
-    <t>0.8073,0.1420,0.0147,0.0069</t>
-  </si>
-  <si>
-    <t>0.5391,0.4736,0.0454,0.0053</t>
-  </si>
-  <si>
-    <t>0.5160,0.4866,0.0360,0.0062</t>
-  </si>
-  <si>
-    <t>0.7364,0.2474,0.0185,0.0041</t>
-  </si>
-  <si>
-    <t>0.2564,0.7755,0.0312,0.0041</t>
-  </si>
-  <si>
-    <t>0.7197,0.2980,0.0108,0.0027</t>
-  </si>
-  <si>
-    <t>0.4752,0.5163,0.0713,0.0080</t>
-  </si>
-  <si>
-    <t>0.3992,0.4458,0.3909,0.0304</t>
-  </si>
-  <si>
-    <t>0.6129,0.3284,0.1218,0.0089</t>
-  </si>
-  <si>
-    <t>0.5781,0.4035,0.0615,0.0075</t>
-  </si>
-  <si>
-    <t>0.3879,0.0076,0.7872,0.0020</t>
-  </si>
-  <si>
-    <t>0.2228,0.0094,0.8796,0.0018</t>
-  </si>
-  <si>
-    <t>0.5710,0.0735,0.5346,0.0095</t>
-  </si>
-  <si>
-    <t>0.0411,0.0076,0.9767,0.0008</t>
-  </si>
-  <si>
-    <t>0.8996,0.0133,0.1483,0.0037</t>
-  </si>
-  <si>
-    <t>0.0975,0.0093,0.9115,0.0031</t>
-  </si>
-  <si>
-    <t>0.6314,0.0133,0.5233,0.0080</t>
-  </si>
-  <si>
-    <t>0.0307,0.2080,0.9215,0.0049</t>
-  </si>
-  <si>
-    <t>0.9252,0.0195,0.0555,0.0029</t>
-  </si>
-  <si>
-    <t>0.9033,0.0122,0.1132,0.0041</t>
-  </si>
-  <si>
-    <t>0.9247,0.0245,0.0602,0.0028</t>
-  </si>
-  <si>
-    <t>0.6544,0.3239,0.0140,0.0033</t>
-  </si>
-  <si>
-    <t>0.2602,0.7665,0.0717,0.0063</t>
-  </si>
-  <si>
-    <t>0.8292,0.0813,0.0071,0.0077</t>
-  </si>
-  <si>
-    <t>0.6739,0.3914,0.0249,0.0030</t>
-  </si>
-  <si>
-    <t>0.7020,0.2678,0.0254,0.0043</t>
-  </si>
-  <si>
-    <t>0.6118,0.3802,0.0250,0.0041</t>
-  </si>
-  <si>
-    <t>0.5913,0.4677,0.0183,0.0027</t>
-  </si>
-  <si>
-    <t>0.6762,0.3496,0.0239,0.0033</t>
-  </si>
-  <si>
-    <t>0.7723,0.0224,0.3489,0.0065</t>
-  </si>
-  <si>
-    <t>0.0583,0.0164,0.9600,0.0012</t>
-  </si>
-  <si>
-    <t>0.0721,0.0057,0.9565,0.0026</t>
-  </si>
-  <si>
-    <t>0.6872,0.0074,0.5098,0.0035</t>
-  </si>
-  <si>
-    <t>0.7895,0.0042,0.4070,0.0016</t>
-  </si>
-  <si>
-    <t>0.4299,0.0376,0.6612,0.0199</t>
-  </si>
-  <si>
-    <t>0.6631,0.0307,0.4182,0.0113</t>
-  </si>
-  <si>
-    <t>0.8992,0.0041,0.2164,0.0027</t>
-  </si>
-  <si>
-    <t>0.9141,0.0392,0.0169,0.0051</t>
-  </si>
-  <si>
-    <t>0.9071,0.0224,0.0553,0.0107</t>
-  </si>
-  <si>
-    <t>0.9362,0.0147,0.0269,0.0114</t>
-  </si>
-  <si>
-    <t>0.8617,0.0266,0.0367,0.0435</t>
-  </si>
-  <si>
-    <t>0.6140,0.0985,0.1273,0.2026</t>
-  </si>
-  <si>
-    <t>0.7480,0.1357,0.1028,0.0192</t>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>0.9638,0.0002,0.0008,0.0589</t>
+  </si>
+  <si>
+    <t>0.0071,0.0019,0.0006,0.9964</t>
+  </si>
+  <si>
+    <t>0.8966,0.0003,0.0003,0.2601</t>
+  </si>
+  <si>
+    <t>0.0948,0.0019,0.0004,0.9757</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0012,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9940,0.0029,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9907,0.0057,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9914,0.0040,0.0010,0.0016</t>
+  </si>
+  <si>
+    <t>0.9966,0.0015,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.8501,0.0117,0.1937,0.0042</t>
+  </si>
+  <si>
+    <t>0.2192,0.0019,0.8980,0.0012</t>
+  </si>
+  <si>
+    <t>0.2144,0.0010,0.8913,0.0010</t>
+  </si>
+  <si>
+    <t>0.0218,0.0055,0.9696,0.0067</t>
+  </si>
+  <si>
+    <t>0.8714,0.0144,0.0760,0.0345</t>
+  </si>
+  <si>
+    <t>0.0020,0.9949,0.0083,0.0006</t>
+  </si>
+  <si>
+    <t>0.0119,0.9849,0.0062,0.0019</t>
+  </si>
+  <si>
+    <t>0.0664,0.9315,0.0200,0.0017</t>
+  </si>
+  <si>
+    <t>0.0242,0.9686,0.0150,0.0020</t>
+  </si>
+  <si>
+    <t>0.0056,0.9922,0.0071,0.0005</t>
+  </si>
+  <si>
+    <t>0.9141,0.0033,0.0678,0.0129</t>
+  </si>
+  <si>
+    <t>0.3880,0.0011,0.6808,0.0067</t>
+  </si>
+  <si>
+    <t>0.0486,0.0013,0.9606,0.0021</t>
+  </si>
+  <si>
+    <t>0.1183,0.0144,0.8696,0.0181</t>
+  </si>
+  <si>
+    <t>0.0451,0.0054,0.8975,0.0589</t>
+  </si>
+  <si>
+    <t>0.1276,0.0023,0.8818,0.0104</t>
+  </si>
+  <si>
+    <t>0.0033,0.0004,0.9885,0.0063</t>
+  </si>
+  <si>
+    <t>0.3382,0.7766,0.0117,0.0165</t>
+  </si>
+  <si>
+    <t>0.5587,0.3304,0.1185,0.0660</t>
+  </si>
+  <si>
+    <t>0.0003,0.0074,0.9989,0.0018</t>
+  </si>
+  <si>
+    <t>0.0250,0.8885,0.1591,0.0006</t>
+  </si>
+  <si>
+    <t>0.7988,0.0767,0.1148,0.0790</t>
+  </si>
+  <si>
+    <t>0.9281,0.0263,0.0416,0.0083</t>
+  </si>
+  <si>
+    <t>0.8688,0.1802,0.0095,0.0015</t>
+  </si>
+  <si>
+    <t>0.0143,0.9677,0.0890,0.0005</t>
+  </si>
+  <si>
+    <t>0.0399,0.0282,0.9095,0.0296</t>
+  </si>
+  <si>
+    <t>0.2539,0.0012,0.5864,0.0447</t>
+  </si>
+  <si>
+    <t>0.1366,0.0053,0.8752,0.0111</t>
+  </si>
+  <si>
+    <t>0.1786,0.0003,0.3263,0.1413</t>
+  </si>
+  <si>
+    <t>0.0080,0.0812,0.9892,0.0027</t>
+  </si>
+  <si>
+    <t>0.0279,0.2207,0.5621,0.0076</t>
+  </si>
+  <si>
+    <t>0.0049,0.0027,0.9895,0.0039</t>
+  </si>
+  <si>
+    <t>0.5112,0.0152,0.0038,0.6415</t>
+  </si>
+  <si>
+    <t>0.0123,0.9605,0.0189,0.0222</t>
+  </si>
+  <si>
+    <t>0.0295,0.9225,0.0918,0.0093</t>
+  </si>
+  <si>
+    <t>0.0026,0.9832,0.0485,0.0083</t>
+  </si>
+  <si>
+    <t>0.0003,0.0021,0.9961,0.0101</t>
+  </si>
+  <si>
+    <t>0.0012,0.0048,0.9956,0.0040</t>
+  </si>
+  <si>
+    <t>0.0234,0.0017,0.9694,0.0068</t>
+  </si>
+  <si>
+    <t>0.0085,0.0016,0.9853,0.0055</t>
+  </si>
+  <si>
+    <t>0.0029,0.0020,0.9947,0.0016</t>
+  </si>
+  <si>
+    <t>0.0020,0.0015,0.9952,0.0013</t>
+  </si>
+  <si>
+    <t>0.9789,0.0168,0.0028,0.0026</t>
+  </si>
+  <si>
+    <t>0.9135,0.0682,0.0067,0.0216</t>
+  </si>
+  <si>
+    <t>0.9878,0.0040,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.0365,0.0541,0.9684,0.0027</t>
+  </si>
+  <si>
+    <t>0.9921,0.0032,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.9739,0.0199,0.0036,0.0024</t>
+  </si>
+  <si>
+    <t>0.9525,0.0596,0.0048,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.0635,0.9954,0.0028</t>
+  </si>
+  <si>
+    <t>0.0029,0.0019,0.9953,0.0020</t>
+  </si>
+  <si>
+    <t>0.0054,0.0120,0.9863,0.0063</t>
+  </si>
+  <si>
+    <t>0.0016,0.7386,0.9796,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.0016,0.9963,0.0034</t>
+  </si>
+  <si>
+    <t>0.0169,0.9541,0.0529,0.0006</t>
+  </si>
+  <si>
+    <t>0.0023,0.9953,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.9625,0.0065,0.0490,0.0031</t>
+  </si>
+  <si>
+    <t>0.9365,0.0253,0.0268,0.0087</t>
+  </si>
+  <si>
+    <t>0.0013,0.0593,0.9928,0.0190</t>
+  </si>
+  <si>
+    <t>0.0084,0.4154,0.9552,0.0029</t>
+  </si>
+  <si>
+    <t>0.0009,0.6097,0.9899,0.0008</t>
+  </si>
+  <si>
+    <t>0.0041,0.9798,0.1825,0.0043</t>
+  </si>
+  <si>
+    <t>0.0028,0.3543,0.9676,0.0021</t>
+  </si>
+  <si>
+    <t>0.0036,0.0007,0.0026,0.9963</t>
+  </si>
+  <si>
+    <t>0.0007,0.0123,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.0340,0.0011,0.0003,0.9919</t>
+  </si>
+  <si>
+    <t>0.0108,0.0006,0.0005,0.9964</t>
+  </si>
+  <si>
+    <t>0.0032,0.0006,0.0021,0.9971</t>
+  </si>
+  <si>
+    <t>0.0035,0.0075,0.0024,0.9962</t>
+  </si>
+  <si>
+    <t>0.0062,0.7862,0.9470,0.0018</t>
+  </si>
+  <si>
+    <t>0.0285,0.0142,0.9702,0.0041</t>
+  </si>
+  <si>
+    <t>0.0094,0.0598,0.9774,0.0043</t>
+  </si>
+  <si>
+    <t>0.0028,0.1160,0.9909,0.0016</t>
+  </si>
+  <si>
+    <t>0.0012,0.8290,0.9650,0.0003</t>
+  </si>
+  <si>
+    <t>0.0051,0.8613,0.5712,0.0011</t>
+  </si>
+  <si>
+    <t>0.9941,0.0025,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9884,0.0138,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.6706,0.4593,0.0085,0.0029</t>
+  </si>
+  <si>
+    <t>0.9735,0.0167,0.0029,0.0038</t>
+  </si>
+  <si>
+    <t>0.9934,0.0017,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.9972,0.0008,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9873,0.0045,0.0035,0.0029</t>
+  </si>
+  <si>
+    <t>0.9881,0.0078,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9954,0.0012,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9971,0.0003,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9963,0.0013,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9912,0.0032,0.0010,0.0031</t>
+  </si>
+  <si>
+    <t>0.9929,0.0042,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9893,0.0028,0.0010,0.0052</t>
+  </si>
+  <si>
+    <t>0.9945,0.0009,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9944,0.0091</t>
+  </si>
+  <si>
+    <t>0.0780,0.0038,0.8945,0.0229</t>
+  </si>
+  <si>
+    <t>0.9563,0.0008,0.0240,0.0092</t>
+  </si>
+  <si>
+    <t>0.0063,0.0005,0.9917,0.0017</t>
+  </si>
+  <si>
+    <t>0.0028,0.9945,0.0072,0.0003</t>
+  </si>
+  <si>
+    <t>0.0112,0.9855,0.0050,0.0005</t>
+  </si>
+  <si>
+    <t>0.0568,0.9330,0.0154,0.0064</t>
+  </si>
+  <si>
+    <t>0.2507,0.7911,0.0304,0.0094</t>
+  </si>
+  <si>
+    <t>0.0037,0.9907,0.0089,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.9974,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.6772,0.3523,0.0408,0.0066</t>
+  </si>
+  <si>
+    <t>0.9039,0.0197,0.0710,0.0127</t>
+  </si>
+  <si>
+    <t>0.0644,0.0009,0.9264,0.0091</t>
+  </si>
+  <si>
+    <t>0.7445,0.0073,0.2105,0.0335</t>
+  </si>
+  <si>
+    <t>0.8347,0.0117,0.1075,0.0439</t>
+  </si>
+  <si>
+    <t>0.0570,0.0083,0.0076,0.9716</t>
+  </si>
+  <si>
+    <t>0.0003,0.9975,0.0137,0.0006</t>
+  </si>
+  <si>
+    <t>0.0018,0.9942,0.0031,0.0019</t>
+  </si>
+  <si>
+    <t>0.0140,0.9678,0.0240,0.0131</t>
+  </si>
+  <si>
+    <t>0.0004,0.5620,0.9884,0.0010</t>
+  </si>
+  <si>
+    <t>0.0129,0.9663,0.1556,0.0005</t>
+  </si>
+  <si>
+    <t>0.8733,0.1256,0.0338,0.0092</t>
+  </si>
+  <si>
+    <t>0.9558,0.0321,0.0178,0.0017</t>
+  </si>
+  <si>
+    <t>0.9566,0.0428,0.0083,0.0044</t>
+  </si>
+  <si>
+    <t>0.9955,0.0008,0.0011,0.0014</t>
+  </si>
+  <si>
+    <t>0.9829,0.0033,0.0029,0.0067</t>
+  </si>
+  <si>
+    <t>0.9790,0.0081,0.0083,0.0028</t>
+  </si>
+  <si>
+    <t>0.9907,0.0012,0.0014,0.0056</t>
+  </si>
+  <si>
+    <t>0.9907,0.0015,0.0085,0.0012</t>
+  </si>
+  <si>
+    <t>0.9882,0.0028,0.0022,0.0052</t>
+  </si>
+  <si>
+    <t>0.9868,0.0042,0.0077,0.0021</t>
+  </si>
+  <si>
+    <t>0.0407,0.0191,0.9526,0.0088</t>
+  </si>
+  <si>
+    <t>0.0024,0.0528,0.9931,0.0013</t>
+  </si>
+  <si>
+    <t>0.0039,0.0057,0.9924,0.0010</t>
+  </si>
+  <si>
+    <t>0.0180,0.0038,0.9851,0.0024</t>
+  </si>
+  <si>
+    <t>0.9636,0.0007,0.0202,0.0075</t>
+  </si>
+  <si>
+    <t>0.8321,0.0027,0.0829,0.0348</t>
+  </si>
+  <si>
+    <t>0.2507,0.0064,0.7428,0.0264</t>
+  </si>
+  <si>
+    <t>0.7771,0.0050,0.1386,0.0495</t>
+  </si>
+  <si>
+    <t>0.0157,0.0007,0.0005,0.9949</t>
+  </si>
+  <si>
+    <t>0.0003,0.0017,0.0002,0.9996</t>
+  </si>
+  <si>
+    <t>0.0023,0.0088,0.0002,0.9983</t>
+  </si>
+  <si>
+    <t>0.0056,0.0001,0.0003,0.9983</t>
+  </si>
+  <si>
+    <t>0.0049,0.5704,0.9401,0.0066</t>
+  </si>
+  <si>
+    <t>0.9921,0.0025,0.0034,0.0009</t>
+  </si>
+  <si>
+    <t>0.8030,0.1802,0.0485,0.0058</t>
+  </si>
+  <si>
+    <t>0.9852,0.0072,0.0018,0.0029</t>
+  </si>
+  <si>
+    <t>0.9001,0.1402,0.0080,0.0011</t>
+  </si>
+  <si>
+    <t>0.9685,0.0006,0.0014,0.0380</t>
+  </si>
+  <si>
+    <t>0.8413,0.0139,0.0036,0.2033</t>
+  </si>
+  <si>
+    <t>0.9827,0.0017,0.0066,0.0058</t>
+  </si>
+  <si>
+    <t>0.0032,0.0196,0.9719,0.1027</t>
+  </si>
+  <si>
+    <t>0.9263,0.0014,0.0019,0.1419</t>
+  </si>
+  <si>
+    <t>0.9842,0.0012,0.0010,0.0119</t>
+  </si>
+  <si>
+    <t>0.7471,0.1760,0.0998,0.0234</t>
+  </si>
+  <si>
+    <t>0.9751,0.0048,0.0009,0.0085</t>
+  </si>
+  <si>
+    <t>0.9605,0.0339,0.0082,0.0026</t>
+  </si>
+  <si>
+    <t>0.4540,0.4723,0.0752,0.0298</t>
+  </si>
+  <si>
+    <t>0.9371,0.0277,0.0371,0.0052</t>
+  </si>
+  <si>
+    <t>0.9732,0.0091,0.0225,0.0007</t>
+  </si>
+  <si>
+    <t>0.9879,0.0065,0.0018,0.0017</t>
+  </si>
+  <si>
+    <t>0.9967,0.0006,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9926,0.0016,0.0012,0.0027</t>
+  </si>
+  <si>
+    <t>0.9938,0.0005,0.0008,0.0041</t>
+  </si>
+  <si>
+    <t>0.9944,0.0004,0.0015,0.0025</t>
+  </si>
+  <si>
+    <t>0.9832,0.0097,0.0018,0.0022</t>
+  </si>
+  <si>
+    <t>0.9922,0.0020,0.0016,0.0022</t>
+  </si>
+  <si>
+    <t>0.9956,0.0006,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.4555,0.6151,0.0045,0.0110</t>
+  </si>
+  <si>
+    <t>0.5432,0.4513,0.0319,0.0009</t>
+  </si>
+  <si>
+    <t>0.8714,0.1376,0.0184,0.0010</t>
+  </si>
+  <si>
+    <t>0.0647,0.0522,0.9493,0.0071</t>
+  </si>
+  <si>
+    <t>0.9665,0.0328,0.0035,0.0026</t>
+  </si>
+  <si>
+    <t>0.9816,0.0012,0.0018,0.0142</t>
+  </si>
+  <si>
+    <t>0.9938,0.0023,0.0021,0.0011</t>
+  </si>
+  <si>
+    <t>0.9778,0.0065,0.0021,0.0067</t>
+  </si>
+  <si>
+    <t>0.0006,0.0157,0.9991,0.0005</t>
+  </si>
+  <si>
+    <t>0.8626,0.0644,0.1040,0.0034</t>
+  </si>
+  <si>
+    <t>0.0037,0.0007,0.9914,0.0029</t>
+  </si>
+  <si>
+    <t>0.0013,0.0198,0.9903,0.0122</t>
+  </si>
+  <si>
+    <t>0.0158,0.0056,0.9816,0.0028</t>
+  </si>
+  <si>
+    <t>0.0009,0.0021,0.9965,0.0061</t>
+  </si>
+  <si>
+    <t>0.0086,0.0076,0.9741,0.0168</t>
+  </si>
+  <si>
+    <t>0.0018,0.0009,0.9955,0.0023</t>
+  </si>
+  <si>
+    <t>0.0068,0.0040,0.9897,0.0036</t>
+  </si>
+  <si>
+    <t>0.3912,0.0104,0.5795,0.0442</t>
+  </si>
+  <si>
+    <t>0.0775,0.0270,0.8900,0.0286</t>
+  </si>
+  <si>
+    <t>0.7147,0.0336,0.3640,0.0189</t>
+  </si>
+  <si>
+    <t>0.2664,0.0769,0.6984,0.0137</t>
+  </si>
+  <si>
+    <t>0.1208,0.0141,0.9050,0.0036</t>
+  </si>
+  <si>
+    <t>0.5140,0.0202,0.5395,0.0070</t>
+  </si>
+  <si>
+    <t>0.6911,0.0157,0.1715,0.0845</t>
+  </si>
+  <si>
+    <t>0.6154,0.0533,0.4328,0.0241</t>
+  </si>
+  <si>
+    <t>0.0484,0.9555,0.0096,0.0015</t>
+  </si>
+  <si>
+    <t>0.0097,0.9861,0.0047,0.0017</t>
+  </si>
+  <si>
+    <t>0.3190,0.8313,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.5812,0.4114,0.0406,0.0011</t>
+  </si>
+  <si>
+    <t>0.8470,0.2398,0.0062,0.0009</t>
+  </si>
+  <si>
+    <t>0.3704,0.1925,0.4480,0.0179</t>
+  </si>
+  <si>
+    <t>0.8395,0.0043,0.1799,0.0124</t>
+  </si>
+  <si>
+    <t>0.9424,0.0008,0.0126,0.0283</t>
+  </si>
+  <si>
+    <t>0.5472,0.0009,0.0779,0.1910</t>
+  </si>
+  <si>
+    <t>0.9063,0.0005,0.0309,0.0237</t>
+  </si>
+  <si>
+    <t>0.0025,0.0010,0.9912,0.0084</t>
+  </si>
+  <si>
+    <t>0.0164,0.0027,0.9361,0.0450</t>
+  </si>
+  <si>
+    <t>0.0822,0.0010,0.8953,0.0101</t>
+  </si>
+  <si>
+    <t>0.0399,0.0028,0.9698,0.0025</t>
+  </si>
+  <si>
+    <t>0.0260,0.0193,0.9371,0.0180</t>
+  </si>
+  <si>
+    <t>0.9906,0.0040,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.9954,0.0019,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9743,0.0184,0.0089,0.0032</t>
+  </si>
+  <si>
+    <t>0.9701,0.0263,0.0062,0.0018</t>
+  </si>
+  <si>
+    <t>0.9838,0.0122,0.0030,0.0018</t>
+  </si>
+  <si>
+    <t>0.9907,0.0046,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.9921,0.0036,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9929,0.0009,0.0026,0.0030</t>
+  </si>
+  <si>
+    <t>0.0020,0.0083,0.9975,0.0004</t>
+  </si>
+  <si>
+    <t>0.1266,0.8144,0.1215,0.0077</t>
+  </si>
+  <si>
+    <t>0.8335,0.0310,0.0885,0.0300</t>
+  </si>
+  <si>
+    <t>0.0015,0.0006,0.9977,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0019,0.9946,0.0190</t>
+  </si>
+  <si>
+    <t>0.0007,0.0153,0.9956,0.0043</t>
+  </si>
+  <si>
+    <t>0.0037,0.0006,0.9964,0.0003</t>
+  </si>
+  <si>
+    <t>0.0074,0.0011,0.9839,0.0081</t>
+  </si>
+  <si>
+    <t>0.0010,0.0014,0.9951,0.0067</t>
+  </si>
+  <si>
+    <t>0.0086,0.0062,0.9796,0.0078</t>
+  </si>
+  <si>
+    <t>0.0242,0.0173,0.9063,0.0891</t>
+  </si>
+  <si>
+    <t>0.8688,0.0006,0.0256,0.0589</t>
+  </si>
+  <si>
+    <t>0.6882,0.0023,0.3014,0.0208</t>
+  </si>
+  <si>
+    <t>0.9851,0.0008,0.0058,0.0041</t>
+  </si>
+  <si>
+    <t>0.9751,0.0221,0.0045,0.0024</t>
+  </si>
+  <si>
+    <t>0.9905,0.0054,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9964,0.0010,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9662,0.0422,0.0040,0.0008</t>
+  </si>
+  <si>
+    <t>0.9950,0.0015,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9917,0.0032,0.0033,0.0015</t>
+  </si>
+  <si>
+    <t>0.9897,0.0089,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.9953,0.0030,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.0125,0.0080,0.9841,0.0022</t>
+  </si>
+  <si>
+    <t>0.0025,0.0038,0.9939,0.0029</t>
+  </si>
+  <si>
+    <t>0.0038,0.0009,0.9893,0.0057</t>
+  </si>
+  <si>
+    <t>0.0408,0.0040,0.9520,0.0068</t>
+  </si>
+  <si>
+    <t>0.0041,0.0007,0.9934,0.0012</t>
+  </si>
+  <si>
+    <t>0.0264,0.0147,0.6155,0.5681</t>
+  </si>
+  <si>
+    <t>0.2601,0.0025,0.8058,0.0068</t>
+  </si>
+  <si>
+    <t>0.0367,0.0088,0.9506,0.0140</t>
+  </si>
+  <si>
+    <t>0.8012,0.0002,0.0005,0.5204</t>
+  </si>
+  <si>
+    <t>0.0134,0.0026,0.0012,0.9935</t>
+  </si>
+  <si>
+    <t>0.0343,0.0006,0.0005,0.9914</t>
+  </si>
+  <si>
+    <t>0.0015,0.0000,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0043,0.0004,0.0002,0.9986</t>
+  </si>
+  <si>
+    <t>0.9666,0.0018,0.0049,0.0256</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,10 +2054,10 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,10 +2110,10 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2362,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2376,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2407,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,10 +2544,10 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,10 +2600,10 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,10 +2614,10 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2701,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,10 +2782,10 @@
         <v>259</v>
       </c>
       <c r="C61" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2841,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2883,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2953,7 @@
         <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2978,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>261</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3121,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3135,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,10 +3356,10 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3415,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,10 +3622,10 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,10 +3636,10 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,10 +3776,10 @@
         <v>259</v>
       </c>
       <c r="C132" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,10 +3818,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3835,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3877,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,10 +4070,10 @@
         <v>259</v>
       </c>
       <c r="C153" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,10 +4252,10 @@
         <v>259</v>
       </c>
       <c r="C166" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,10 +4266,10 @@
         <v>259</v>
       </c>
       <c r="C167" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4378,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4406,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,10 +4476,10 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4549,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4563,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4703,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4717,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4756,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4843,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,10 +4980,10 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,10 +5008,10 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5151,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5165,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,10 +5232,10 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5361,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5375,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
